--- a/docs/self-checklist.xlsx
+++ b/docs/self-checklist.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>2026-10-23 · 증빙 위치: docs/checklist/, docs/assets/, docs/rag-before-after.md</t>
+          <t>2026-10-23 · 실제 서버·GMS로 실행 · 증빙 위치: docs/checklist/</t>
         </is>
       </c>
       <c r="D6" s="34" t="n"/>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="H9" s="33" t="inlineStr">
         <is>
-          <t>c01_f2001_counts.png</t>
+          <t>01_색인_건수_일치.png</t>
         </is>
       </c>
       <c r="I9" s="33" t="inlineStr">
         <is>
-          <t>법령 382 = Chroma 382, 판례 880 일치</t>
+          <t>법령 382 = Chroma 382, 판례 913 일치</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="H10" s="33" t="inlineStr">
         <is>
-          <t>c02_f2002_reindex.png</t>
+          <t>02_재색인_청크수_유지.png</t>
         </is>
       </c>
       <c r="I10" s="33" t="inlineStr">
         <is>
-          <t>382 → 382, 임베딩만 고정 벡터</t>
+          <t>GMS 임베딩 두 번 색인 382 → 382</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="H11" s="33" t="inlineStr">
         <is>
-          <t>c03_c04_enrichment_cache.png</t>
+          <t>03_04_검색어_선별_재질문_캐시.png</t>
         </is>
       </c>
       <c r="I11" s="33" t="inlineStr">
         <is>
-          <t>검색어 7개, indexed 1·filtered 2·rejected 10</t>
+          <t>검색어 8개, 후보 4건 중 indexed 1·rejected 3</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="H12" s="33" t="inlineStr">
         <is>
-          <t>c03_c04_enrichment_cache.png</t>
+          <t>03_04_검색어_선별_재질문_캐시.png</t>
         </is>
       </c>
       <c r="I12" s="33" t="inlineStr">
         <is>
-          <t>33.0초 수집 1건 → 11.7초 cache_hit</t>
+          <t>판례 수집 6.5초(1건) → 1.0초 cache_hit</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="H13" s="33" t="inlineStr">
         <is>
-          <t>c05_f2005_chunk_sizes.png</t>
+          <t>05_청크설정별_청크수.png</t>
         </is>
       </c>
       <c r="I13" s="33" t="inlineStr">
         <is>
-          <t>법령 382→397→432, 판례 652→912→1265</t>
+          <t>법령 382→397, 판례 652→912</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="H14" s="33" t="inlineStr">
         <is>
-          <t>c06_c16_topk_mmr.png</t>
+          <t>06_16_TopK_유사도_MMR_비교.png</t>
         </is>
       </c>
       <c r="I14" s="33" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="H15" s="33" t="inlineStr">
         <is>
-          <t>c07_f2007_langgraph.png</t>
+          <t>07_LangGraph_노드구성.png</t>
         </is>
       </c>
       <c r="I15" s="33" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="H16" s="33" t="inlineStr">
         <is>
-          <t>c08_c14_c19_real_answer.png</t>
+          <t>08_14_19_실제답변_근거목록_2.png</t>
         </is>
       </c>
       <c r="I16" s="33" t="inlineStr">
         <is>
-          <t>[근거 6][근거 2] = 목록 2건, 법령·판례 표시</t>
+          <t>본문 근거 4개 = 목록 4건, 법령·판례 표시</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="H17" s="33" t="inlineStr">
         <is>
-          <t>safelaw-refusal.png</t>
+          <t>09_근거없음_답변거부.png</t>
         </is>
       </c>
       <c r="I17" s="33" t="inlineStr">
         <is>
-          <t>10-22 실제 서버, 근거 부족 안내</t>
+          <t>점심 메뉴 질문 → 근거 부족 안내</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="H18" s="33" t="inlineStr">
         <is>
-          <t>c10_f2009_isolation_tests.png</t>
+          <t>10_대화분리_1~3.png (3장)</t>
         </is>
       </c>
       <c r="I18" s="33" t="inlineStr">
         <is>
-          <t>대화 분리 테스트 3개 통과</t>
+          <t>제27조 2개 → 제26조 0개 → 복귀 2개</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H19" s="33" t="inlineStr">
         <is>
-          <t>safelaw-condition-search.png</t>
+          <t>11_조건탐색_결과.png</t>
         </is>
       </c>
       <c r="I19" s="33" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H20" s="33" t="inlineStr">
         <is>
-          <t>safelaw-issue-checklist.png</t>
+          <t>12_쟁점체크리스트_근거.png</t>
         </is>
       </c>
       <c r="I20" s="33" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="H21" s="33" t="inlineStr">
         <is>
-          <t>c13_*.png (4장)</t>
+          <t>13_진행상태·색인없음·키없음 (3장)</t>
         </is>
       </c>
       <c r="I21" s="33" t="inlineStr">
         <is>
-          <t>가짜 백엔드로 화면 재현(GMS 미호출)</t>
+          <t>실제 서버: 처리 중, 색인 없음, 키 없음</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="H22" s="33" t="inlineStr">
         <is>
-          <t>c08_c14_c19_real_answer.png</t>
+          <t>08_14_19_실제답변_근거목록_2.png</t>
         </is>
       </c>
       <c r="I22" s="33" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="H23" s="33" t="inlineStr">
         <is>
-          <t>safelaw-web-frontend.png</t>
+          <t>15_웹화면_질문답변근거.png</t>
         </is>
       </c>
       <c r="I23" s="33" t="inlineStr">
         <is>
-          <t>질문·답변·근거 표시 (10-22)</t>
+          <t>웹 화면 질문·답변·근거·체크리스트</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="H24" s="33" t="inlineStr">
         <is>
-          <t>c06_c16_topk_mmr.png</t>
+          <t>06_16_TopK_유사도_MMR_비교.png</t>
         </is>
       </c>
       <c r="I24" s="33" t="inlineStr">
         <is>
-          <t>Top-k 5에서 5번째 법령이 달라짐</t>
+          <t>Top-k 5에서 순서·판례 1건이 달라짐</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H25" s="33" t="inlineStr">
         <is>
-          <t>rag-before-after.md</t>
+          <t>17_18_RAG_전후비교_문서.png</t>
         </is>
       </c>
       <c r="I25" s="33" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="H26" s="33" t="inlineStr">
         <is>
-          <t>rag-before-after.md</t>
+          <t>17_18_RAG_전후비교_문서.png</t>
         </is>
       </c>
       <c r="I26" s="33" t="inlineStr">
         <is>
-          <t>docs/ 폴더에 포함</t>
+          <t>docs/rag-before-after.md</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="H27" s="33" t="inlineStr">
         <is>
-          <t>c08_c14_c19_real_answer.png</t>
+          <t>08_14_19_실제답변_근거목록_2.png</t>
         </is>
       </c>
       <c r="I27" s="33" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="H28" s="33" t="inlineStr">
         <is>
-          <t>c20_nf2001_response_time.png</t>
+          <t>20_처리시간_첫질문_두번째질문.png</t>
         </is>
       </c>
       <c r="I28" s="33" t="inlineStr">
         <is>
-          <t>8.3~16.7초, 새 판례 수집 시 +33초</t>
+          <t>첫 질문 15.2초, 두 번째 15.1초</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="H29" s="33" t="inlineStr">
         <is>
-          <t>c21_*.png (2장)</t>
+          <t>21_키_검색_결과.png, 21_오류_화면.png</t>
         </is>
       </c>
       <c r="I29" s="33" t="inlineStr">
         <is>
-          <t>키 값 0건, 오류 화면은 고정 문구</t>
+          <t>키 값 0건, 실제 오류에도 고정 문구</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="H30" s="33" t="inlineStr">
         <is>
-          <t>c22_nf2005_modules.png</t>
+          <t>22_모듈_구성.png</t>
         </is>
       </c>
       <c r="I30" s="33" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="H31" s="33" t="inlineStr">
         <is>
-          <t>c23_nf2006_api_etiquette.png</t>
+          <t>23_외부호출_재시도_헤더.png</t>
         </is>
       </c>
       <c r="I31" s="33" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H32" s="33" t="inlineStr">
         <is>
-          <t>c24_nf2007_sources.png</t>
+          <t>24_출처_이용조건.png</t>
         </is>
       </c>
       <c r="I32" s="33" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H34" s="33" t="inlineStr">
         <is>
-          <t>docs/checklist, docs/assets</t>
+          <t>docs/checklist/ (25장)</t>
         </is>
       </c>
       <c r="I34" s="33" t="inlineStr">
